--- a/db/templates/incoming_invoice_default.xlsx
+++ b/db/templates/incoming_invoice_default.xlsx
@@ -10,6 +10,9 @@
     <sheet name="Incoming Invoice" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Incoming Invoice'!$1:$13</definedName>
+  </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
@@ -818,6 +821,10 @@
     <mergeCell ref="A14:B14"/>
   </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
+    <evenFooter>&amp;CPage &amp;P of &amp;N</evenFooter>
+  </headerFooter>
 </worksheet>
 </file>
 

--- a/db/templates/incoming_invoice_default.xlsx
+++ b/db/templates/incoming_invoice_default.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>{{vendor.name}}</t>
   </si>
@@ -303,6 +303,27 @@
   </si>
   <si>
     <t>Free-text notes, blank if unset</t>
+  </si>
+  <si>
+    <t>Export info</t>
+  </si>
+  <si>
+    <t>{{export.generatedDate}}</t>
+  </si>
+  <si>
+    <t>Date this file was exported (not the invoice's own date), in the organization's date format</t>
+  </si>
+  <si>
+    <t>{{export.generatedTime}}</t>
+  </si>
+  <si>
+    <t>Time this file was exported, 24-hour HH:MM, server time</t>
+  </si>
+  <si>
+    <t>&amp;P (page number) / &amp;N (total pages)</t>
+  </si>
+  <si>
+    <t>Native Excel/LibreOffice codes, not a {{}} placeholder — only work inside this sheet's own Page Layout ▸ Header/Footer, never in a regular cell, since the page count isn't known until export. The default footer already shows "Page &amp;P of &amp;N" on every page; edit it in Excel/LibreOffice's own header/footer editor to move or restyle it</t>
   </si>
 </sst>
 </file>
@@ -1137,12 +1158,42 @@
         <v>94</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A41:C41"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/incoming_invoice_default.xlsx
+++ b/db/templates/incoming_invoice_default.xlsx
@@ -791,16 +791,16 @@
       <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G14" t="s">
